--- a/clinical_tables/clinical_ZIKV.xlsx
+++ b/clinical_tables/clinical_ZIKV.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="68">
   <si>
     <t>Category</t>
   </si>
@@ -67,22 +67,19 @@
     <t>15-19</t>
   </si>
   <si>
-    <t>20-29</t>
-  </si>
-  <si>
-    <t>30-39</t>
-  </si>
-  <si>
-    <t>40-49</t>
+    <t>20-39</t>
+  </si>
+  <si>
+    <t>40-59</t>
   </si>
   <si>
     <t>5-9</t>
   </si>
   <si>
-    <t>50-59</t>
-  </si>
-  <si>
-    <t>60-69</t>
+    <t>60-64</t>
+  </si>
+  <si>
+    <t>65-69</t>
   </si>
   <si>
     <t>70-79</t>
@@ -94,10 +91,7 @@
     <t>&lt;1</t>
   </si>
   <si>
-    <t>Dengue c/ complicacoes (antigo)</t>
-  </si>
-  <si>
-    <t>Dengue classico (schema antigo)</t>
+    <t>Confirmado</t>
   </si>
   <si>
     <t>Ignorado/NA</t>
@@ -572,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1">
@@ -618,37 +612,37 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>10611</v>
+        <v>8136</v>
       </c>
       <c r="C2">
-        <v>1558</v>
+        <v>928</v>
       </c>
       <c r="D2">
-        <v>1014</v>
+        <v>426</v>
       </c>
       <c r="E2">
-        <v>1681</v>
+        <v>614</v>
       </c>
       <c r="F2">
-        <v>804</v>
+        <v>325</v>
       </c>
       <c r="G2">
-        <v>858</v>
+        <v>327</v>
       </c>
       <c r="H2">
-        <v>1789</v>
+        <v>464</v>
       </c>
       <c r="I2">
-        <v>1390</v>
+        <v>357</v>
       </c>
       <c r="J2">
-        <v>1593</v>
+        <v>246</v>
       </c>
       <c r="K2">
-        <v>1141</v>
+        <v>211</v>
       </c>
       <c r="L2">
-        <v>626</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -656,37 +650,37 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>15934</v>
+        <v>12346</v>
       </c>
       <c r="C3">
-        <v>1862</v>
+        <v>1095</v>
       </c>
       <c r="D3">
-        <v>1177</v>
+        <v>486</v>
       </c>
       <c r="E3">
-        <v>2216</v>
+        <v>743</v>
       </c>
       <c r="F3">
-        <v>1214</v>
+        <v>508</v>
       </c>
       <c r="G3">
-        <v>1170</v>
+        <v>406</v>
       </c>
       <c r="H3">
-        <v>2570</v>
+        <v>674</v>
       </c>
       <c r="I3">
-        <v>2510</v>
+        <v>563</v>
       </c>
       <c r="J3">
-        <v>2776</v>
+        <v>336</v>
       </c>
       <c r="K3">
-        <v>1759</v>
+        <v>271</v>
       </c>
       <c r="L3">
-        <v>1019</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -694,37 +688,37 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>24566</v>
+        <v>18601</v>
       </c>
       <c r="C4">
-        <v>3317</v>
+        <v>1818</v>
       </c>
       <c r="D4">
-        <v>1875</v>
+        <v>755</v>
       </c>
       <c r="E4">
-        <v>2811</v>
+        <v>903</v>
       </c>
       <c r="F4">
-        <v>1457</v>
+        <v>568</v>
       </c>
       <c r="G4">
-        <v>1373</v>
+        <v>430</v>
       </c>
       <c r="H4">
-        <v>2816</v>
+        <v>639</v>
       </c>
       <c r="I4">
-        <v>3290</v>
+        <v>584</v>
       </c>
       <c r="J4">
-        <v>3580</v>
+        <v>399</v>
       </c>
       <c r="K4">
-        <v>2089</v>
+        <v>301</v>
       </c>
       <c r="L4">
-        <v>1295</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -732,37 +726,37 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>62471</v>
+        <v>91715</v>
       </c>
       <c r="C5">
-        <v>8478</v>
+        <v>7867</v>
       </c>
       <c r="D5">
-        <v>4834</v>
+        <v>3513</v>
       </c>
       <c r="E5">
-        <v>7260</v>
+        <v>4241</v>
       </c>
       <c r="F5">
-        <v>4283</v>
+        <v>2960</v>
       </c>
       <c r="G5">
-        <v>3934</v>
+        <v>2233</v>
       </c>
       <c r="H5">
-        <v>7088</v>
+        <v>3013</v>
       </c>
       <c r="I5">
-        <v>7521</v>
+        <v>2295</v>
       </c>
       <c r="J5">
-        <v>9273</v>
+        <v>1854</v>
       </c>
       <c r="K5">
-        <v>5191</v>
+        <v>1180</v>
       </c>
       <c r="L5">
-        <v>2739</v>
+        <v>733</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -770,37 +764,37 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>57636</v>
+        <v>54309</v>
       </c>
       <c r="C6">
-        <v>6654</v>
+        <v>3606</v>
       </c>
       <c r="D6">
-        <v>4011</v>
+        <v>1792</v>
       </c>
       <c r="E6">
-        <v>6092</v>
+        <v>1932</v>
       </c>
       <c r="F6">
-        <v>4402</v>
+        <v>1801</v>
       </c>
       <c r="G6">
-        <v>3845</v>
+        <v>1500</v>
       </c>
       <c r="H6">
-        <v>6521</v>
+        <v>1908</v>
       </c>
       <c r="I6">
-        <v>6421</v>
+        <v>1533</v>
       </c>
       <c r="J6">
-        <v>7671</v>
+        <v>1201</v>
       </c>
       <c r="K6">
-        <v>4276</v>
+        <v>877</v>
       </c>
       <c r="L6">
-        <v>2060</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -808,37 +802,37 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>39126</v>
+        <v>10115</v>
       </c>
       <c r="C7">
-        <v>3498</v>
+        <v>1003</v>
       </c>
       <c r="D7">
-        <v>2334</v>
+        <v>449</v>
       </c>
       <c r="E7">
-        <v>3268</v>
+        <v>779</v>
       </c>
       <c r="F7">
-        <v>3041</v>
+        <v>447</v>
       </c>
       <c r="G7">
-        <v>2718</v>
+        <v>397</v>
       </c>
       <c r="H7">
-        <v>4892</v>
+        <v>618</v>
       </c>
       <c r="I7">
-        <v>5212</v>
+        <v>501</v>
       </c>
       <c r="J7">
-        <v>6189</v>
+        <v>317</v>
       </c>
       <c r="K7">
-        <v>3368</v>
+        <v>240</v>
       </c>
       <c r="L7">
-        <v>1604</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -846,37 +840,37 @@
         <v>18</v>
       </c>
       <c r="B8">
-        <v>13290</v>
+        <v>7216</v>
       </c>
       <c r="C8">
-        <v>1760</v>
+        <v>431</v>
       </c>
       <c r="D8">
-        <v>1139</v>
+        <v>238</v>
       </c>
       <c r="E8">
-        <v>2186</v>
+        <v>235</v>
       </c>
       <c r="F8">
-        <v>1110</v>
+        <v>201</v>
       </c>
       <c r="G8">
-        <v>1070</v>
+        <v>199</v>
       </c>
       <c r="H8">
-        <v>2397</v>
+        <v>270</v>
       </c>
       <c r="I8">
-        <v>2132</v>
+        <v>198</v>
       </c>
       <c r="J8">
-        <v>2288</v>
+        <v>195</v>
       </c>
       <c r="K8">
-        <v>1628</v>
+        <v>140</v>
       </c>
       <c r="L8">
-        <v>941</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -884,37 +878,37 @@
         <v>19</v>
       </c>
       <c r="B9">
-        <v>27737</v>
+        <v>4899</v>
       </c>
       <c r="C9">
-        <v>2171</v>
+        <v>294</v>
       </c>
       <c r="D9">
-        <v>1688</v>
+        <v>139</v>
       </c>
       <c r="E9">
-        <v>2084</v>
+        <v>172</v>
       </c>
       <c r="F9">
-        <v>2026</v>
+        <v>146</v>
       </c>
       <c r="G9">
-        <v>1913</v>
+        <v>144</v>
       </c>
       <c r="H9">
-        <v>3438</v>
+        <v>184</v>
       </c>
       <c r="I9">
-        <v>3500</v>
+        <v>172</v>
       </c>
       <c r="J9">
-        <v>4385</v>
+        <v>128</v>
       </c>
       <c r="K9">
-        <v>2594</v>
+        <v>108</v>
       </c>
       <c r="L9">
-        <v>1107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -922,37 +916,37 @@
         <v>20</v>
       </c>
       <c r="B10">
-        <v>14741</v>
+        <v>4978</v>
       </c>
       <c r="C10">
-        <v>1180</v>
+        <v>253</v>
       </c>
       <c r="D10">
-        <v>894</v>
+        <v>185</v>
       </c>
       <c r="E10">
-        <v>1058</v>
+        <v>187</v>
       </c>
       <c r="F10">
-        <v>988</v>
+        <v>167</v>
       </c>
       <c r="G10">
-        <v>955</v>
+        <v>140</v>
       </c>
       <c r="H10">
-        <v>1976</v>
+        <v>210</v>
       </c>
       <c r="I10">
-        <v>2056</v>
+        <v>145</v>
       </c>
       <c r="J10">
-        <v>2798</v>
+        <v>180</v>
       </c>
       <c r="K10">
-        <v>1737</v>
+        <v>119</v>
       </c>
       <c r="L10">
-        <v>679</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -960,37 +954,37 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>5974</v>
+        <v>1994</v>
       </c>
       <c r="C11">
-        <v>458</v>
+        <v>105</v>
       </c>
       <c r="D11">
-        <v>407</v>
+        <v>44</v>
       </c>
       <c r="E11">
-        <v>454</v>
+        <v>45</v>
       </c>
       <c r="F11">
-        <v>453</v>
+        <v>70</v>
       </c>
       <c r="G11">
-        <v>437</v>
+        <v>48</v>
       </c>
       <c r="H11">
-        <v>966</v>
+        <v>100</v>
       </c>
       <c r="I11">
-        <v>899</v>
+        <v>68</v>
       </c>
       <c r="J11">
-        <v>1313</v>
+        <v>83</v>
       </c>
       <c r="K11">
-        <v>799</v>
+        <v>50</v>
       </c>
       <c r="L11">
-        <v>324</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -998,75 +992,37 @@
         <v>22</v>
       </c>
       <c r="B12">
-        <v>2352</v>
+        <v>4957</v>
       </c>
       <c r="C12">
-        <v>174</v>
+        <v>764</v>
       </c>
       <c r="D12">
-        <v>128</v>
+        <v>421</v>
       </c>
       <c r="E12">
-        <v>159</v>
+        <v>470</v>
       </c>
       <c r="F12">
-        <v>193</v>
+        <v>360</v>
       </c>
       <c r="G12">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="H12">
-        <v>370</v>
+        <v>222</v>
       </c>
       <c r="I12">
-        <v>329</v>
+        <v>195</v>
       </c>
       <c r="J12">
-        <v>522</v>
+        <v>175</v>
       </c>
       <c r="K12">
-        <v>330</v>
+        <v>168</v>
       </c>
       <c r="L12">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13">
-        <v>7026</v>
-      </c>
-      <c r="C13">
-        <v>1574</v>
-      </c>
-      <c r="D13">
-        <v>1083</v>
-      </c>
-      <c r="E13">
-        <v>1231</v>
-      </c>
-      <c r="F13">
-        <v>896</v>
-      </c>
-      <c r="G13">
-        <v>660</v>
-      </c>
-      <c r="H13">
-        <v>981</v>
-      </c>
-      <c r="I13">
-        <v>743</v>
-      </c>
-      <c r="J13">
-        <v>924</v>
-      </c>
-      <c r="K13">
-        <v>852</v>
-      </c>
-      <c r="L13">
-        <v>423</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1">
@@ -1119,192 +1075,154 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2">
-        <v>62198</v>
+        <v>141766</v>
       </c>
       <c r="C2">
-        <v>14520</v>
+        <v>9578</v>
       </c>
       <c r="D2">
-        <v>12136</v>
+        <v>4399</v>
       </c>
       <c r="E2">
-        <v>20179</v>
+        <v>4307</v>
       </c>
       <c r="F2">
-        <v>13314</v>
+        <v>3093</v>
       </c>
       <c r="G2">
-        <v>13035</v>
+        <v>4308</v>
       </c>
       <c r="H2">
-        <v>27502</v>
+        <v>3536</v>
       </c>
       <c r="I2">
-        <v>29392</v>
+        <v>4036</v>
       </c>
       <c r="J2">
-        <v>38198</v>
+        <v>2068</v>
       </c>
       <c r="K2">
-        <v>22099</v>
+        <v>1875</v>
       </c>
       <c r="L2">
-        <v>10849</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>141766</v>
+        <v>6656</v>
       </c>
       <c r="C3">
-        <v>9578</v>
+        <v>1011</v>
       </c>
       <c r="D3">
-        <v>4399</v>
+        <v>732</v>
       </c>
       <c r="E3">
-        <v>4307</v>
+        <v>903</v>
       </c>
       <c r="F3">
-        <v>3093</v>
+        <v>450</v>
       </c>
       <c r="G3">
-        <v>4308</v>
+        <v>320</v>
       </c>
       <c r="H3">
-        <v>3536</v>
+        <v>576</v>
       </c>
       <c r="I3">
-        <v>4036</v>
+        <v>356</v>
       </c>
       <c r="J3">
-        <v>2068</v>
+        <v>537</v>
       </c>
       <c r="K3">
-        <v>1875</v>
+        <v>433</v>
       </c>
       <c r="L3">
-        <v>655</v>
+        <v>754</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4">
-        <v>6656</v>
+        <v>70844</v>
       </c>
       <c r="C4">
-        <v>1011</v>
+        <v>7575</v>
       </c>
       <c r="D4">
-        <v>732</v>
+        <v>3317</v>
       </c>
       <c r="E4">
-        <v>903</v>
+        <v>5111</v>
       </c>
       <c r="F4">
-        <v>450</v>
+        <v>4010</v>
       </c>
       <c r="G4">
-        <v>320</v>
+        <v>1427</v>
       </c>
       <c r="H4">
-        <v>576</v>
+        <v>4190</v>
       </c>
       <c r="I4">
-        <v>356</v>
+        <v>2070</v>
       </c>
       <c r="J4">
-        <v>537</v>
+        <v>2509</v>
       </c>
       <c r="K4">
-        <v>433</v>
+        <v>1353</v>
       </c>
       <c r="L4">
-        <v>776</v>
+        <v>688</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5">
-        <v>70844</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>7575</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>3317</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>5111</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>4010</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1427</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>4190</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>2070</v>
+        <v>149</v>
       </c>
       <c r="J5">
-        <v>2509</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>1353</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>149</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1357,121 +1275,121 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2">
-        <v>178720</v>
+        <v>132911</v>
       </c>
       <c r="C2">
-        <v>15871</v>
+        <v>8309</v>
       </c>
       <c r="D2">
-        <v>7277</v>
+        <v>2850</v>
       </c>
       <c r="E2">
-        <v>12105</v>
+        <v>3052</v>
       </c>
       <c r="F2">
-        <v>4488</v>
+        <v>1005</v>
       </c>
       <c r="G2">
-        <v>4873</v>
+        <v>642</v>
       </c>
       <c r="H2">
-        <v>8309</v>
+        <v>1221</v>
       </c>
       <c r="I2">
-        <v>13075</v>
+        <v>742</v>
       </c>
       <c r="J2">
-        <v>10373</v>
+        <v>438</v>
       </c>
       <c r="K2">
-        <v>4005</v>
+        <v>372</v>
       </c>
       <c r="L2">
-        <v>1656</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>77419</v>
+        <v>77074</v>
       </c>
       <c r="C3">
-        <v>8627</v>
+        <v>8526</v>
       </c>
       <c r="D3">
-        <v>4076</v>
+        <v>4025</v>
       </c>
       <c r="E3">
-        <v>6075</v>
+        <v>5951</v>
       </c>
       <c r="F3">
-        <v>4493</v>
+        <v>4422</v>
       </c>
       <c r="G3">
-        <v>1793</v>
+        <v>1724</v>
       </c>
       <c r="H3">
-        <v>5000</v>
+        <v>4739</v>
       </c>
       <c r="I3">
-        <v>2734</v>
+        <v>2427</v>
       </c>
       <c r="J3">
-        <v>3348</v>
+        <v>3025</v>
       </c>
       <c r="K3">
-        <v>1852</v>
+        <v>1758</v>
       </c>
       <c r="L3">
-        <v>1474</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>25325</v>
+        <v>9281</v>
       </c>
       <c r="C4">
-        <v>8186</v>
+        <v>1329</v>
       </c>
       <c r="D4">
-        <v>9231</v>
+        <v>1573</v>
       </c>
       <c r="E4">
-        <v>12320</v>
+        <v>1318</v>
       </c>
       <c r="F4">
-        <v>11886</v>
+        <v>2126</v>
       </c>
       <c r="G4">
-        <v>12424</v>
+        <v>3689</v>
       </c>
       <c r="H4">
-        <v>22495</v>
+        <v>2342</v>
       </c>
       <c r="I4">
-        <v>19982</v>
+        <v>3311</v>
       </c>
       <c r="J4">
-        <v>29545</v>
+        <v>1651</v>
       </c>
       <c r="K4">
-        <v>19882</v>
+        <v>1531</v>
       </c>
       <c r="L4">
-        <v>9823</v>
+        <v>580</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1495,16 +1413,16 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="J5">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1557,136 +1475,136 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2">
-        <v>186214</v>
+        <v>135903</v>
       </c>
       <c r="C2">
-        <v>21536</v>
+        <v>9002</v>
       </c>
       <c r="D2">
-        <v>14417</v>
+        <v>4153</v>
       </c>
       <c r="E2">
-        <v>21849</v>
+        <v>3847</v>
       </c>
       <c r="F2">
-        <v>12141</v>
+        <v>2808</v>
       </c>
       <c r="G2">
-        <v>15491</v>
+        <v>3929</v>
       </c>
       <c r="H2">
-        <v>25564</v>
+        <v>3143</v>
       </c>
       <c r="I2">
-        <v>22253</v>
+        <v>3461</v>
       </c>
       <c r="J2">
-        <v>30809</v>
+        <v>1775</v>
       </c>
       <c r="K2">
-        <v>20034</v>
+        <v>1660</v>
       </c>
       <c r="L2">
-        <v>10296</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3">
-        <v>6433</v>
+        <v>3581</v>
       </c>
       <c r="C3">
-        <v>1107</v>
+        <v>333</v>
       </c>
       <c r="D3">
-        <v>984</v>
+        <v>186</v>
       </c>
       <c r="E3">
-        <v>1340</v>
+        <v>438</v>
       </c>
       <c r="F3">
-        <v>3096</v>
+        <v>165</v>
       </c>
       <c r="G3">
-        <v>944</v>
+        <v>199</v>
       </c>
       <c r="H3">
-        <v>3624</v>
+        <v>316</v>
       </c>
       <c r="I3">
-        <v>6875</v>
+        <v>395</v>
       </c>
       <c r="J3">
-        <v>5612</v>
+        <v>210</v>
       </c>
       <c r="K3">
-        <v>1636</v>
+        <v>164</v>
       </c>
       <c r="L3">
-        <v>721</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>88643</v>
+        <v>79721</v>
       </c>
       <c r="C4">
-        <v>9918</v>
+        <v>8811</v>
       </c>
       <c r="D4">
-        <v>5065</v>
+        <v>4093</v>
       </c>
       <c r="E4">
-        <v>7180</v>
+        <v>6025</v>
       </c>
       <c r="F4">
-        <v>5541</v>
+        <v>4560</v>
       </c>
       <c r="G4">
-        <v>2573</v>
+        <v>1909</v>
       </c>
       <c r="H4">
-        <v>6487</v>
+        <v>4836</v>
       </c>
       <c r="I4">
-        <v>4621</v>
+        <v>2590</v>
       </c>
       <c r="J4">
-        <v>6351</v>
+        <v>3117</v>
       </c>
       <c r="K4">
-        <v>3777</v>
+        <v>1828</v>
       </c>
       <c r="L4">
-        <v>1847</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>43</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>7</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1709,45 +1627,45 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B6">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>126</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="H6">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>225</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>129</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>63</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1771,16 +1689,16 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>2077</v>
+        <v>152</v>
       </c>
       <c r="J7">
-        <v>315</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>187</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1833,1028 +1751,1028 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>1531</v>
+        <v>119</v>
       </c>
       <c r="C2">
-        <v>295</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>365</v>
+        <v>102</v>
       </c>
       <c r="E2">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="F2">
-        <v>305</v>
+        <v>47</v>
       </c>
       <c r="G2">
-        <v>622</v>
+        <v>279</v>
       </c>
       <c r="H2">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="I2">
-        <v>908</v>
+        <v>128</v>
       </c>
       <c r="J2">
-        <v>958</v>
+        <v>122</v>
       </c>
       <c r="K2">
-        <v>1279</v>
+        <v>53</v>
       </c>
       <c r="L2">
-        <v>266</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B3">
-        <v>8153</v>
+        <v>6422</v>
       </c>
       <c r="C3">
-        <v>361</v>
+        <v>237</v>
       </c>
       <c r="D3">
-        <v>447</v>
+        <v>153</v>
       </c>
       <c r="E3">
-        <v>1337</v>
+        <v>692</v>
       </c>
       <c r="F3">
-        <v>272</v>
+        <v>147</v>
       </c>
       <c r="G3">
-        <v>450</v>
+        <v>286</v>
       </c>
       <c r="H3">
-        <v>1273</v>
+        <v>609</v>
       </c>
       <c r="I3">
-        <v>197</v>
+        <v>68</v>
       </c>
       <c r="J3">
-        <v>234</v>
+        <v>71</v>
       </c>
       <c r="K3">
-        <v>174</v>
+        <v>53</v>
       </c>
       <c r="L3">
-        <v>158</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4">
-        <v>1057</v>
+        <v>413</v>
       </c>
       <c r="C4">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>121</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="H4">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="I4">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="J4">
-        <v>420</v>
+        <v>270</v>
       </c>
       <c r="K4">
-        <v>176</v>
+        <v>26</v>
       </c>
       <c r="L4">
-        <v>96</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B5">
-        <v>6023</v>
+        <v>4507</v>
       </c>
       <c r="C5">
-        <v>699</v>
+        <v>430</v>
       </c>
       <c r="D5">
-        <v>469</v>
+        <v>360</v>
       </c>
       <c r="E5">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="F5">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="G5">
-        <v>223</v>
+        <v>113</v>
       </c>
       <c r="H5">
-        <v>356</v>
+        <v>241</v>
       </c>
       <c r="I5">
-        <v>367</v>
+        <v>264</v>
       </c>
       <c r="J5">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="K5">
-        <v>231</v>
+        <v>29</v>
       </c>
       <c r="L5">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B6">
-        <v>58938</v>
+        <v>52063</v>
       </c>
       <c r="C6">
-        <v>3026</v>
+        <v>2390</v>
       </c>
       <c r="D6">
-        <v>1547</v>
+        <v>819</v>
       </c>
       <c r="E6">
-        <v>3123</v>
+        <v>2161</v>
       </c>
       <c r="F6">
-        <v>5044</v>
+        <v>3784</v>
       </c>
       <c r="G6">
-        <v>2120</v>
+        <v>1051</v>
       </c>
       <c r="H6">
-        <v>2944</v>
+        <v>1116</v>
       </c>
       <c r="I6">
-        <v>4394</v>
+        <v>1814</v>
       </c>
       <c r="J6">
-        <v>4691</v>
+        <v>1206</v>
       </c>
       <c r="K6">
-        <v>916</v>
+        <v>299</v>
       </c>
       <c r="L6">
-        <v>585</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B7">
-        <v>8670</v>
+        <v>4337</v>
       </c>
       <c r="C7">
-        <v>3569</v>
+        <v>1490</v>
       </c>
       <c r="D7">
-        <v>632</v>
+        <v>91</v>
       </c>
       <c r="E7">
-        <v>633</v>
+        <v>121</v>
       </c>
       <c r="F7">
-        <v>768</v>
+        <v>229</v>
       </c>
       <c r="G7">
-        <v>1701</v>
+        <v>389</v>
       </c>
       <c r="H7">
-        <v>2896</v>
+        <v>416</v>
       </c>
       <c r="I7">
-        <v>1147</v>
+        <v>68</v>
       </c>
       <c r="J7">
-        <v>2255</v>
+        <v>89</v>
       </c>
       <c r="K7">
-        <v>1738</v>
+        <v>73</v>
       </c>
       <c r="L7">
-        <v>2132</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B8">
-        <v>1050</v>
+        <v>408</v>
       </c>
       <c r="C8">
-        <v>284</v>
+        <v>74</v>
       </c>
       <c r="D8">
-        <v>172</v>
+        <v>43</v>
       </c>
       <c r="E8">
-        <v>431</v>
+        <v>209</v>
       </c>
       <c r="F8">
-        <v>2692</v>
+        <v>55</v>
       </c>
       <c r="G8">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="H8">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="I8">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="K8">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B9">
-        <v>2909</v>
+        <v>2405</v>
       </c>
       <c r="C9">
-        <v>576</v>
+        <v>370</v>
       </c>
       <c r="D9">
-        <v>592</v>
+        <v>250</v>
       </c>
       <c r="E9">
-        <v>1368</v>
+        <v>593</v>
       </c>
       <c r="F9">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>1068</v>
+        <v>252</v>
       </c>
       <c r="I9">
-        <v>13284</v>
+        <v>1127</v>
       </c>
       <c r="J9">
-        <v>5427</v>
+        <v>87</v>
       </c>
       <c r="K9">
-        <v>1230</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>213</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B10">
-        <v>11290</v>
+        <v>10465</v>
       </c>
       <c r="C10">
-        <v>4882</v>
+        <v>3960</v>
       </c>
       <c r="D10">
-        <v>2071</v>
+        <v>1015</v>
       </c>
       <c r="E10">
-        <v>1058</v>
+        <v>254</v>
       </c>
       <c r="F10">
-        <v>186</v>
+        <v>50</v>
       </c>
       <c r="G10">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="H10">
-        <v>290</v>
+        <v>68</v>
       </c>
       <c r="I10">
-        <v>445</v>
+        <v>236</v>
       </c>
       <c r="J10">
-        <v>3416</v>
+        <v>141</v>
       </c>
       <c r="K10">
-        <v>301</v>
+        <v>45</v>
       </c>
       <c r="L10">
-        <v>410</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B11">
-        <v>5031</v>
+        <v>4645</v>
       </c>
       <c r="C11">
-        <v>630</v>
+        <v>532</v>
       </c>
       <c r="D11">
+        <v>176</v>
+      </c>
+      <c r="E11">
+        <v>358</v>
+      </c>
+      <c r="F11">
+        <v>161</v>
+      </c>
+      <c r="G11">
+        <v>54</v>
+      </c>
+      <c r="H11">
+        <v>166</v>
+      </c>
+      <c r="I11">
+        <v>205</v>
+      </c>
+      <c r="J11">
+        <v>334</v>
+      </c>
+      <c r="K11">
+        <v>184</v>
+      </c>
+      <c r="L11">
         <v>212</v>
-      </c>
-      <c r="E11">
-        <v>464</v>
-      </c>
-      <c r="F11">
-        <v>183</v>
-      </c>
-      <c r="G11">
-        <v>105</v>
-      </c>
-      <c r="H11">
-        <v>1315</v>
-      </c>
-      <c r="I11">
-        <v>1889</v>
-      </c>
-      <c r="J11">
-        <v>1845</v>
-      </c>
-      <c r="K11">
-        <v>1105</v>
-      </c>
-      <c r="L11">
-        <v>1600</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12">
-        <v>26509</v>
+        <v>22684</v>
       </c>
       <c r="C12">
-        <v>2621</v>
+        <v>2212</v>
       </c>
       <c r="D12">
-        <v>1099</v>
+        <v>576</v>
       </c>
       <c r="E12">
-        <v>426</v>
+        <v>234</v>
       </c>
       <c r="F12">
-        <v>842</v>
+        <v>441</v>
       </c>
       <c r="G12">
-        <v>401</v>
+        <v>231</v>
       </c>
       <c r="H12">
-        <v>400</v>
+        <v>168</v>
       </c>
       <c r="I12">
-        <v>726</v>
+        <v>509</v>
       </c>
       <c r="J12">
-        <v>2541</v>
+        <v>471</v>
       </c>
       <c r="K12">
-        <v>3282</v>
+        <v>1343</v>
       </c>
       <c r="L12">
-        <v>631</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B13">
-        <v>3874</v>
+        <v>1825</v>
       </c>
       <c r="C13">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="D13">
-        <v>358</v>
+        <v>136</v>
       </c>
       <c r="E13">
-        <v>647</v>
+        <v>65</v>
       </c>
       <c r="F13">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="G13">
-        <v>415</v>
+        <v>55</v>
       </c>
       <c r="H13">
-        <v>1267</v>
+        <v>32</v>
       </c>
       <c r="I13">
-        <v>1335</v>
+        <v>127</v>
       </c>
       <c r="J13">
-        <v>1124</v>
+        <v>86</v>
       </c>
       <c r="K13">
-        <v>3720</v>
+        <v>359</v>
       </c>
       <c r="L13">
-        <v>1826</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B14">
-        <v>20482</v>
+        <v>13609</v>
       </c>
       <c r="C14">
-        <v>1853</v>
+        <v>743</v>
       </c>
       <c r="D14">
-        <v>1018</v>
+        <v>160</v>
       </c>
       <c r="E14">
-        <v>3215</v>
+        <v>661</v>
       </c>
       <c r="F14">
-        <v>1378</v>
+        <v>345</v>
       </c>
       <c r="G14">
-        <v>401</v>
+        <v>97</v>
       </c>
       <c r="H14">
-        <v>545</v>
+        <v>43</v>
       </c>
       <c r="I14">
-        <v>1041</v>
+        <v>154</v>
       </c>
       <c r="J14">
-        <v>1157</v>
+        <v>172</v>
       </c>
       <c r="K14">
-        <v>520</v>
+        <v>42</v>
       </c>
       <c r="L14">
-        <v>290</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15">
-        <v>6632</v>
+        <v>4732</v>
       </c>
       <c r="C15">
-        <v>1456</v>
+        <v>702</v>
       </c>
       <c r="D15">
-        <v>808</v>
+        <v>234</v>
       </c>
       <c r="E15">
-        <v>402</v>
+        <v>168</v>
       </c>
       <c r="F15">
-        <v>440</v>
+        <v>211</v>
       </c>
       <c r="G15">
-        <v>252</v>
+        <v>46</v>
       </c>
       <c r="H15">
-        <v>571</v>
+        <v>73</v>
       </c>
       <c r="I15">
-        <v>460</v>
+        <v>60</v>
       </c>
       <c r="J15">
-        <v>903</v>
+        <v>128</v>
       </c>
       <c r="K15">
-        <v>528</v>
+        <v>55</v>
       </c>
       <c r="L15">
-        <v>350</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B16">
-        <v>4179</v>
+        <v>3009</v>
       </c>
       <c r="C16">
-        <v>289</v>
+        <v>125</v>
       </c>
       <c r="D16">
-        <v>687</v>
+        <v>421</v>
       </c>
       <c r="E16">
-        <v>709</v>
+        <v>464</v>
       </c>
       <c r="F16">
-        <v>624</v>
+        <v>358</v>
       </c>
       <c r="G16">
-        <v>2528</v>
+        <v>1717</v>
       </c>
       <c r="H16">
-        <v>2547</v>
+        <v>606</v>
       </c>
       <c r="I16">
-        <v>293</v>
+        <v>121</v>
       </c>
       <c r="J16">
-        <v>2181</v>
+        <v>97</v>
       </c>
       <c r="K16">
-        <v>212</v>
+        <v>19</v>
       </c>
       <c r="L16">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B17">
-        <v>3954</v>
+        <v>648</v>
       </c>
       <c r="C17">
-        <v>488</v>
+        <v>53</v>
       </c>
       <c r="D17">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="E17">
-        <v>343</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="G17">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="H17">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="I17">
-        <v>167</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>211</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B18">
-        <v>1539</v>
+        <v>458</v>
       </c>
       <c r="C18">
-        <v>344</v>
+        <v>43</v>
       </c>
       <c r="D18">
-        <v>796</v>
+        <v>136</v>
       </c>
       <c r="E18">
-        <v>3879</v>
+        <v>268</v>
       </c>
       <c r="F18">
-        <v>2145</v>
+        <v>159</v>
       </c>
       <c r="G18">
-        <v>4414</v>
+        <v>338</v>
       </c>
       <c r="H18">
-        <v>5151</v>
+        <v>216</v>
       </c>
       <c r="I18">
-        <v>1192</v>
+        <v>76</v>
       </c>
       <c r="J18">
-        <v>3546</v>
+        <v>193</v>
       </c>
       <c r="K18">
-        <v>1860</v>
+        <v>98</v>
       </c>
       <c r="L18">
-        <v>1269</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B19">
-        <v>538</v>
+        <v>226</v>
       </c>
       <c r="C19">
-        <v>525</v>
+        <v>94</v>
       </c>
       <c r="D19">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="E19">
-        <v>178</v>
+        <v>63</v>
       </c>
       <c r="F19">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G19">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="H19">
-        <v>382</v>
+        <v>155</v>
       </c>
       <c r="I19">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="J19">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="K19">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="L19">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B20">
-        <v>4479</v>
+        <v>3652</v>
       </c>
       <c r="C20">
-        <v>683</v>
+        <v>573</v>
       </c>
       <c r="D20">
-        <v>1201</v>
+        <v>597</v>
       </c>
       <c r="E20">
-        <v>1665</v>
+        <v>1179</v>
       </c>
       <c r="F20">
-        <v>1569</v>
+        <v>539</v>
       </c>
       <c r="G20">
-        <v>919</v>
+        <v>467</v>
       </c>
       <c r="H20">
-        <v>8048</v>
+        <v>3482</v>
       </c>
       <c r="I20">
-        <v>1408</v>
+        <v>843</v>
       </c>
       <c r="J20">
-        <v>3093</v>
+        <v>1164</v>
       </c>
       <c r="K20">
-        <v>1784</v>
+        <v>771</v>
       </c>
       <c r="L20">
-        <v>945</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B21">
-        <v>885</v>
+        <v>169</v>
       </c>
       <c r="C21">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="D21">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="E21">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>331</v>
+        <v>69</v>
       </c>
       <c r="G21">
-        <v>265</v>
+        <v>62</v>
       </c>
       <c r="H21">
-        <v>497</v>
+        <v>83</v>
       </c>
       <c r="I21">
-        <v>253</v>
+        <v>58</v>
       </c>
       <c r="J21">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="K21">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B22">
-        <v>83562</v>
+        <v>73691</v>
       </c>
       <c r="C22">
-        <v>2959</v>
+        <v>2636</v>
       </c>
       <c r="D22">
-        <v>4229</v>
+        <v>2533</v>
       </c>
       <c r="E22">
-        <v>2859</v>
+        <v>1524</v>
       </c>
       <c r="F22">
-        <v>313</v>
+        <v>170</v>
       </c>
       <c r="G22">
-        <v>194</v>
+        <v>57</v>
       </c>
       <c r="H22">
-        <v>213</v>
+        <v>35</v>
       </c>
       <c r="I22">
-        <v>307</v>
+        <v>2</v>
       </c>
       <c r="J22">
-        <v>714</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B23">
-        <v>1881</v>
+        <v>919</v>
       </c>
       <c r="C23">
-        <v>516</v>
+        <v>133</v>
       </c>
       <c r="D23">
-        <v>271</v>
+        <v>42</v>
       </c>
       <c r="E23">
-        <v>441</v>
+        <v>111</v>
       </c>
       <c r="F23">
-        <v>588</v>
+        <v>127</v>
       </c>
       <c r="G23">
-        <v>294</v>
+        <v>70</v>
       </c>
       <c r="H23">
-        <v>303</v>
+        <v>43</v>
       </c>
       <c r="I23">
-        <v>496</v>
+        <v>47</v>
       </c>
       <c r="J23">
-        <v>2425</v>
+        <v>82</v>
       </c>
       <c r="K23">
-        <v>2575</v>
+        <v>78</v>
       </c>
       <c r="L23">
-        <v>589</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24">
+        <v>169</v>
+      </c>
+      <c r="C24">
+        <v>208</v>
+      </c>
+      <c r="D24">
+        <v>19</v>
+      </c>
+      <c r="E24">
+        <v>23</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
+        <v>29</v>
+      </c>
+      <c r="H24">
+        <v>7</v>
+      </c>
+      <c r="I24">
         <v>57</v>
       </c>
-      <c r="B24">
-        <v>362</v>
-      </c>
-      <c r="C24">
-        <v>855</v>
-      </c>
-      <c r="D24">
-        <v>155</v>
-      </c>
-      <c r="E24">
-        <v>191</v>
-      </c>
-      <c r="F24">
-        <v>74</v>
-      </c>
-      <c r="G24">
-        <v>194</v>
-      </c>
-      <c r="H24">
-        <v>117</v>
-      </c>
-      <c r="I24">
-        <v>300</v>
-      </c>
       <c r="J24">
-        <v>523</v>
+        <v>24</v>
       </c>
       <c r="K24">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="L24">
-        <v>55</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B25">
-        <v>350</v>
+        <v>76</v>
       </c>
       <c r="C25">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="D25">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="E25">
-        <v>206</v>
+        <v>23</v>
       </c>
       <c r="F25">
-        <v>224</v>
+        <v>35</v>
       </c>
       <c r="G25">
-        <v>162</v>
+        <v>25</v>
       </c>
       <c r="H25">
-        <v>544</v>
+        <v>44</v>
       </c>
       <c r="I25">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>199</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>193</v>
+        <v>3</v>
       </c>
       <c r="L25">
-        <v>98</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B26">
-        <v>10414</v>
+        <v>5310</v>
       </c>
       <c r="C26">
-        <v>1670</v>
+        <v>353</v>
       </c>
       <c r="D26">
-        <v>1440</v>
+        <v>277</v>
       </c>
       <c r="E26">
-        <v>3461</v>
+        <v>609</v>
       </c>
       <c r="F26">
-        <v>1163</v>
+        <v>122</v>
       </c>
       <c r="G26">
-        <v>966</v>
+        <v>60</v>
       </c>
       <c r="H26">
-        <v>1084</v>
+        <v>44</v>
       </c>
       <c r="I26">
-        <v>1048</v>
+        <v>50</v>
       </c>
       <c r="J26">
-        <v>1989</v>
+        <v>153</v>
       </c>
       <c r="K26">
-        <v>2003</v>
+        <v>15</v>
       </c>
       <c r="L26">
-        <v>467</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B27">
-        <v>872</v>
+        <v>229</v>
       </c>
       <c r="C27">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D27">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>435</v>
+        <v>46</v>
       </c>
       <c r="F27">
-        <v>528</v>
+        <v>191</v>
       </c>
       <c r="G27">
-        <v>1142</v>
+        <v>366</v>
       </c>
       <c r="H27">
-        <v>1366</v>
+        <v>158</v>
       </c>
       <c r="I27">
-        <v>770</v>
+        <v>223</v>
       </c>
       <c r="J27">
-        <v>910</v>
+        <v>21</v>
       </c>
       <c r="K27">
-        <v>190</v>
+        <v>12</v>
       </c>
       <c r="L27">
-        <v>97</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B28">
-        <v>6300</v>
+        <v>2076</v>
       </c>
       <c r="C28">
-        <v>3274</v>
+        <v>624</v>
       </c>
       <c r="D28">
-        <v>1336</v>
+        <v>209</v>
       </c>
       <c r="E28">
-        <v>2470</v>
+        <v>283</v>
       </c>
       <c r="F28">
-        <v>322</v>
+        <v>30</v>
       </c>
       <c r="G28">
-        <v>788</v>
+        <v>90</v>
       </c>
       <c r="H28">
-        <v>2177</v>
+        <v>175</v>
       </c>
       <c r="I28">
-        <v>3085</v>
+        <v>313</v>
       </c>
       <c r="J28">
-        <v>1974</v>
+        <v>63</v>
       </c>
       <c r="K28">
-        <v>735</v>
+        <v>46</v>
       </c>
       <c r="L28">
-        <v>597</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2907,197 +2825,197 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B2">
-        <v>6566</v>
+        <v>4000</v>
       </c>
       <c r="C2">
-        <v>1679</v>
+        <v>566</v>
       </c>
       <c r="D2">
-        <v>949</v>
+        <v>242</v>
       </c>
       <c r="E2">
-        <v>1407</v>
+        <v>325</v>
       </c>
       <c r="F2">
-        <v>573</v>
+        <v>179</v>
       </c>
       <c r="G2">
-        <v>470</v>
+        <v>98</v>
       </c>
       <c r="H2">
-        <v>745</v>
+        <v>141</v>
       </c>
       <c r="I2">
-        <v>544</v>
+        <v>76</v>
       </c>
       <c r="J2">
-        <v>969</v>
+        <v>80</v>
       </c>
       <c r="K2">
-        <v>671</v>
+        <v>53</v>
       </c>
       <c r="L2">
-        <v>200</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B3">
-        <v>9818</v>
+        <v>6402</v>
       </c>
       <c r="C3">
-        <v>2289</v>
+        <v>752</v>
       </c>
       <c r="D3">
-        <v>1236</v>
+        <v>386</v>
       </c>
       <c r="E3">
-        <v>2070</v>
+        <v>557</v>
       </c>
       <c r="F3">
-        <v>753</v>
+        <v>232</v>
       </c>
       <c r="G3">
-        <v>602</v>
+        <v>112</v>
       </c>
       <c r="H3">
-        <v>1070</v>
+        <v>203</v>
       </c>
       <c r="I3">
-        <v>822</v>
+        <v>104</v>
       </c>
       <c r="J3">
-        <v>1371</v>
+        <v>137</v>
       </c>
       <c r="K3">
-        <v>945</v>
+        <v>80</v>
       </c>
       <c r="L3">
-        <v>263</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B4">
-        <v>9203</v>
+        <v>5592</v>
       </c>
       <c r="C4">
-        <v>2142</v>
+        <v>664</v>
       </c>
       <c r="D4">
-        <v>1165</v>
+        <v>370</v>
       </c>
       <c r="E4">
-        <v>1988</v>
+        <v>533</v>
       </c>
       <c r="F4">
-        <v>659</v>
+        <v>175</v>
       </c>
       <c r="G4">
-        <v>626</v>
+        <v>123</v>
       </c>
       <c r="H4">
-        <v>955</v>
+        <v>167</v>
       </c>
       <c r="I4">
-        <v>797</v>
+        <v>102</v>
       </c>
       <c r="J4">
-        <v>1347</v>
+        <v>136</v>
       </c>
       <c r="K4">
-        <v>992</v>
+        <v>80</v>
       </c>
       <c r="L4">
-        <v>223</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B5">
-        <v>1143</v>
+        <v>779</v>
       </c>
       <c r="C5">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="D5">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="F5">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="I5">
-        <v>132</v>
+        <v>22</v>
       </c>
       <c r="J5">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="K5">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B6">
-        <v>43108</v>
+        <v>35409</v>
       </c>
       <c r="C6">
-        <v>3032</v>
+        <v>2276</v>
       </c>
       <c r="D6">
-        <v>1721</v>
+        <v>1144</v>
       </c>
       <c r="E6">
-        <v>2003</v>
+        <v>1125</v>
       </c>
       <c r="F6">
-        <v>3031</v>
+        <v>1001</v>
       </c>
       <c r="G6">
-        <v>1149</v>
+        <v>438</v>
       </c>
       <c r="H6">
-        <v>1790</v>
+        <v>622</v>
       </c>
       <c r="I6">
-        <v>2039</v>
+        <v>439</v>
       </c>
       <c r="J6">
-        <v>1928</v>
+        <v>382</v>
       </c>
       <c r="K6">
-        <v>729</v>
+        <v>162</v>
       </c>
       <c r="L6">
-        <v>357</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>11</v>
@@ -3106,13 +3024,13 @@
         <v>1</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3135,78 +3053,78 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B8">
-        <v>82511</v>
+        <v>64956</v>
       </c>
       <c r="C8">
-        <v>9189</v>
+        <v>5507</v>
       </c>
       <c r="D8">
-        <v>5803</v>
+        <v>2248</v>
       </c>
       <c r="E8">
-        <v>7940</v>
+        <v>2719</v>
       </c>
       <c r="F8">
-        <v>5317</v>
+        <v>2232</v>
       </c>
       <c r="G8">
-        <v>6279</v>
+        <v>2284</v>
       </c>
       <c r="H8">
-        <v>13100</v>
+        <v>2890</v>
       </c>
       <c r="I8">
-        <v>12883</v>
+        <v>2301</v>
       </c>
       <c r="J8">
-        <v>16303</v>
+        <v>1686</v>
       </c>
       <c r="K8">
-        <v>8826</v>
+        <v>1155</v>
       </c>
       <c r="L8">
-        <v>4716</v>
+        <v>695</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B9">
-        <v>129104</v>
+        <v>102117</v>
       </c>
       <c r="C9">
-        <v>14191</v>
+        <v>8326</v>
       </c>
       <c r="D9">
-        <v>9640</v>
+        <v>4030</v>
       </c>
       <c r="E9">
-        <v>14970</v>
+        <v>5015</v>
       </c>
       <c r="F9">
-        <v>10482</v>
+        <v>3712</v>
       </c>
       <c r="G9">
-        <v>9918</v>
+        <v>2984</v>
       </c>
       <c r="H9">
-        <v>18045</v>
+        <v>4255</v>
       </c>
       <c r="I9">
-        <v>18786</v>
+        <v>3567</v>
       </c>
       <c r="J9">
-        <v>21295</v>
+        <v>2680</v>
       </c>
       <c r="K9">
-        <v>13549</v>
+        <v>2132</v>
       </c>
       <c r="L9">
-        <v>7177</v>
+        <v>1255</v>
       </c>
     </row>
   </sheetData>
@@ -3259,75 +3177,75 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B2">
-        <v>189769</v>
+        <v>146661</v>
       </c>
       <c r="C2">
-        <v>22862</v>
+        <v>12302</v>
       </c>
       <c r="D2">
-        <v>13669</v>
+        <v>5525</v>
       </c>
       <c r="E2">
-        <v>20417</v>
+        <v>6820</v>
       </c>
       <c r="F2">
-        <v>13252</v>
+        <v>4895</v>
       </c>
       <c r="G2">
-        <v>12011</v>
+        <v>3906</v>
       </c>
       <c r="H2">
-        <v>22289</v>
+        <v>5168</v>
       </c>
       <c r="I2">
-        <v>21277</v>
+        <v>3909</v>
       </c>
       <c r="J2">
-        <v>26449</v>
+        <v>3128</v>
       </c>
       <c r="K2">
-        <v>15525</v>
+        <v>2225</v>
       </c>
       <c r="L2">
-        <v>7383</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="C3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>5</v>
       </c>
-      <c r="H3">
-        <v>5</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
       <c r="J3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -3335,40 +3253,40 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B4">
-        <v>91344</v>
+        <v>72288</v>
       </c>
       <c r="C4">
-        <v>9801</v>
+        <v>5844</v>
       </c>
       <c r="D4">
-        <v>6908</v>
+        <v>2921</v>
       </c>
       <c r="E4">
-        <v>10046</v>
+        <v>3470</v>
       </c>
       <c r="F4">
-        <v>7600</v>
+        <v>2648</v>
       </c>
       <c r="G4">
-        <v>7074</v>
+        <v>2148</v>
       </c>
       <c r="H4">
-        <v>13510</v>
+        <v>3133</v>
       </c>
       <c r="I4">
-        <v>14718</v>
+        <v>2697</v>
       </c>
       <c r="J4">
-        <v>16847</v>
+        <v>1985</v>
       </c>
       <c r="K4">
-        <v>10237</v>
+        <v>1439</v>
       </c>
       <c r="L4">
-        <v>5588</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
